--- a/assets/modele_kpi_multifeuilles_mis_a_jour.xlsx
+++ b/assets/modele_kpi_multifeuilles_mis_a_jour.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
   <si>
     <t>date</t>
   </si>
@@ -124,9 +124,6 @@
     <t>transactions</t>
   </si>
   <si>
-    <t>score_discipline</t>
-  </si>
-  <si>
     <t>Nom</t>
   </si>
   <si>
@@ -164,6 +161,9 @@
   </si>
   <si>
     <t>Taux digitalisation (%)</t>
+  </si>
+  <si>
+    <t>Score discipline (%)</t>
   </si>
 </sst>
 </file>
@@ -588,10 +588,10 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2190,10 +2190,10 @@
         <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -3252,13 +3252,13 @@
         <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -4434,7 +4434,7 @@
         <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5254,254 +5254,842 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2">
         <v>45383</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3">
+        <f>IF(OR(C2=0,E2=0,G2=0),0,((B2/C2)*0.4+(D2/E2)*0.3+(1-F2/G2)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="2">
         <v>45384</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <f>IF(OR(C3=0,E3=0,G3=0),0,((B3/C3)*0.4+(D3/E3)*0.3+(1-F3/G3)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="2">
         <v>45385</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <f>IF(OR(C4=0,E4=0,G4=0),0,((B4/C4)*0.4+(D4/E4)*0.3+(1-F4/G4)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="2">
         <v>45386</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <f>IF(OR(C5=0,E5=0,G5=0),0,((B5/C5)*0.4+(D5/E5)*0.3+(1-F5/G5)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="2">
         <v>45387</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <f>IF(OR(C6=0,E6=0,G6=0),0,((B6/C6)*0.4+(D6/E6)*0.3+(1-F6/G6)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="2">
         <v>45388</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <f>IF(OR(C7=0,E7=0,G7=0),0,((B7/C7)*0.4+(D7/E7)*0.3+(1-F7/G7)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="2">
         <v>45389</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <f>IF(OR(C8=0,E8=0,G8=0),0,((B8/C8)*0.4+(D8/E8)*0.3+(1-F8/G8)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="2">
         <v>45390</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <f>IF(OR(C9=0,E9=0,G9=0),0,((B9/C9)*0.4+(D9/E9)*0.3+(1-F9/G9)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="2">
         <v>45391</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <f>IF(OR(C10=0,E10=0,G10=0),0,((B10/C10)*0.4+(D10/E10)*0.3+(1-F10/G10)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="2">
         <v>45392</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:2">
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <f>IF(OR(C11=0,E11=0,G11=0),0,((B11/C11)*0.4+(D11/E11)*0.3+(1-F11/G11)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="2">
         <v>45393</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <f>IF(OR(C12=0,E12=0,G12=0),0,((B12/C12)*0.4+(D12/E12)*0.3+(1-F12/G12)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="2">
         <v>45394</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <f>IF(OR(C13=0,E13=0,G13=0),0,((B13/C13)*0.4+(D13/E13)*0.3+(1-F13/G13)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="2">
         <v>45395</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:2">
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <f>IF(OR(C14=0,E14=0,G14=0),0,((B14/C14)*0.4+(D14/E14)*0.3+(1-F14/G14)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="2">
         <v>45396</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:2">
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <f>IF(OR(C15=0,E15=0,G15=0),0,((B15/C15)*0.4+(D15/E15)*0.3+(1-F15/G15)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="2">
         <v>45397</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
+        <f>IF(OR(C16=0,E16=0,G16=0),0,((B16/C16)*0.4+(D16/E16)*0.3+(1-F16/G16)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="2">
         <v>45398</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <f>IF(OR(C17=0,E17=0,G17=0),0,((B17/C17)*0.4+(D17/E17)*0.3+(1-F17/G17)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="2">
         <v>45399</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <f>IF(OR(C18=0,E18=0,G18=0),0,((B18/C18)*0.4+(D18/E18)*0.3+(1-F18/G18)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="2">
         <v>45400</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <f>IF(OR(C19=0,E19=0,G19=0),0,((B19/C19)*0.4+(D19/E19)*0.3+(1-F19/G19)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="2">
         <v>45401</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <f>IF(OR(C20=0,E20=0,G20=0),0,((B20/C20)*0.4+(D20/E20)*0.3+(1-F20/G20)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="2">
         <v>45402</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <f>IF(OR(C21=0,E21=0,G21=0),0,((B21/C21)*0.4+(D21/E21)*0.3+(1-F21/G21)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="2">
         <v>45403</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:2">
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <f>IF(OR(C22=0,E22=0,G22=0),0,((B22/C22)*0.4+(D22/E22)*0.3+(1-F22/G22)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="2">
         <v>45404</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <f>IF(OR(C23=0,E23=0,G23=0),0,((B23/C23)*0.4+(D23/E23)*0.3+(1-F23/G23)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="2">
         <v>45405</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <f>IF(OR(C24=0,E24=0,G24=0),0,((B24/C24)*0.4+(D24/E24)*0.3+(1-F24/G24)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="2">
         <v>45406</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:2">
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <f>IF(OR(C25=0,E25=0,G25=0),0,((B25/C25)*0.4+(D25/E25)*0.3+(1-F25/G25)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="2">
         <v>45407</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <f>IF(OR(C26=0,E26=0,G26=0),0,((B26/C26)*0.4+(D26/E26)*0.3+(1-F26/G26)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="2">
         <v>45408</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:2">
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <f>IF(OR(C27=0,E27=0,G27=0),0,((B27/C27)*0.4+(D27/E27)*0.3+(1-F27/G27)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="2">
         <v>45409</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <f>IF(OR(C28=0,E28=0,G28=0),0,((B28/C28)*0.4+(D28/E28)*0.3+(1-F28/G28)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="2">
         <v>45410</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:2">
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <f>IF(OR(C29=0,E29=0,G29=0),0,((B29/C29)*0.4+(D29/E29)*0.3+(1-F29/G29)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="2">
         <v>45411</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:2">
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3">
+        <f>IF(OR(C30=0,E30=0,G30=0),0,((B30/C30)*0.4+(D30/E30)*0.3+(1-F30/G30)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="2">
         <v>45412</v>
       </c>
       <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3">
+        <f>IF(OR(C31=0,E31=0,G31=0),0,((B31/C31)*0.4+(D31/E31)*0.3+(1-F31/G31)*0.2)/0.9)</f>
         <v>0</v>
       </c>
     </row>
@@ -5685,19 +6273,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>38</v>
-      </c>
-      <c r="F1" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/assets/modele_kpi_multifeuilles_mis_a_jour.xlsx
+++ b/assets/modele_kpi_multifeuilles_mis_a_jour.xlsx
@@ -13,14 +13,15 @@
     <sheet name="Fintech" sheetId="4" r:id="rId4"/>
     <sheet name="Discipline" sheetId="5" r:id="rId5"/>
     <sheet name="KPI Hebdo" sheetId="6" r:id="rId6"/>
-    <sheet name="Bénéficiaires" sheetId="7" r:id="rId7"/>
+    <sheet name="Rapport Motos" sheetId="7" r:id="rId7"/>
+    <sheet name="Bénéficiaires" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
   <si>
     <t>FINANCIER — Données de remboursement</t>
   </si>
@@ -141,6 +142,21 @@
     <t>Versement hebdomadaire
 (reçu / attendu)
 [AUTO]</t>
+  </si>
+  <si>
+    <t>RAPPORT MOTOS - Versements par moto</t>
+  </si>
+  <si>
+    <t>Une ligne par moto et par date. Exemple moto_id: MOTO-1002.</t>
+  </si>
+  <si>
+    <t>moto_id</t>
+  </si>
+  <si>
+    <t>versement_attendu</t>
+  </si>
+  <si>
+    <t>versement_recu</t>
   </si>
   <si>
     <t>BÉNÉFICIAIRES — Répertoire des bénéficiaires</t>
@@ -3200,6 +3216,295 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="4" width="22.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="22" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" ht="30" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="5">
+        <v>45383</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="5">
+        <v>45384</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5">
+        <v>45385</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="5">
+        <v>45386</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="5">
+        <v>45387</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5">
+        <v>45388</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5">
+        <v>45389</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="5">
+        <v>45390</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="5">
+        <v>45391</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="5">
+        <v>45392</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="5">
+        <v>45393</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="5">
+        <v>45394</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="5">
+        <v>45395</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="5">
+        <v>45396</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="5">
+        <v>45397</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="5">
+        <v>45398</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="5">
+        <v>45399</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="5">
+        <v>45400</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="5">
+        <v>45401</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="5">
+        <v>45402</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="5">
+        <v>45403</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="5">
+        <v>45404</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="5">
+        <v>45405</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="5">
+        <v>45406</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="5">
+        <v>45407</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="5">
+        <v>45408</v>
+      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="5">
+        <v>45409</v>
+      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="5">
+        <v>45410</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="5">
+        <v>45411</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="5">
+        <v>45412</v>
+      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3208,7 +3513,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3221,19 +3526,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
